--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0307</v>
+        <v>0.00567</v>
       </c>
       <c r="E2">
-        <v>0.0127</v>
+        <v>-0.0118</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="L2">
-        <v>0.4306569343065694</v>
+        <v>0.4289772727272727</v>
       </c>
       <c r="M2">
-        <v>8.07</v>
+        <v>9.74</v>
       </c>
       <c r="N2">
-        <v>0.04385869565217392</v>
+        <v>0.06243589743589744</v>
       </c>
       <c r="O2">
-        <v>0.6838983050847457</v>
+        <v>0.6450331125827815</v>
       </c>
       <c r="P2">
-        <v>2.9</v>
+        <v>5.42</v>
       </c>
       <c r="Q2">
-        <v>0.01576086956521739</v>
+        <v>0.03474358974358974</v>
       </c>
       <c r="R2">
-        <v>0.2457627118644068</v>
+        <v>0.3589403973509934</v>
       </c>
       <c r="S2">
-        <v>5.17</v>
+        <v>4.32</v>
       </c>
       <c r="T2">
-        <v>0.6406443618339529</v>
+        <v>0.4435318275154004</v>
       </c>
       <c r="U2">
-        <v>90.5</v>
+        <v>116.2</v>
       </c>
       <c r="V2">
-        <v>0.4918478260869565</v>
+        <v>0.7448717948717949</v>
       </c>
       <c r="W2">
-        <v>0.0960912052117264</v>
+        <v>0.1193675889328063</v>
       </c>
       <c r="X2">
-        <v>0.03798119039409924</v>
+        <v>0.07348037806243042</v>
       </c>
       <c r="Y2">
-        <v>0.05811001481762716</v>
+        <v>0.04588721087037589</v>
       </c>
       <c r="Z2">
-        <v>0.2589547301767319</v>
+        <v>0.4443883348062113</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03326073346042226</v>
+        <v>0.07253347726182223</v>
       </c>
       <c r="AC2">
-        <v>-0.03326073346042226</v>
+        <v>-0.07253347726182223</v>
       </c>
       <c r="AD2">
-        <v>49.9</v>
+        <v>19.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>49.9</v>
+        <v>19.2</v>
       </c>
       <c r="AG2">
-        <v>-40.6</v>
+        <v>-97</v>
       </c>
       <c r="AH2">
-        <v>0.2133390337751176</v>
+        <v>0.1095890410958904</v>
       </c>
       <c r="AI2">
-        <v>0.2828798185941043</v>
+        <v>0.1270681667769689</v>
       </c>
       <c r="AJ2">
-        <v>-0.2831241283124128</v>
+        <v>-1.64406779661017</v>
       </c>
       <c r="AK2">
-        <v>-0.4726426076833527</v>
+        <v>-2.779369627507163</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0307</v>
+        <v>0.00567</v>
       </c>
       <c r="E3">
-        <v>0.0127</v>
+        <v>-0.0118</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>11.8</v>
+        <v>15.1</v>
       </c>
       <c r="L3">
-        <v>0.4306569343065694</v>
+        <v>0.4289772727272727</v>
       </c>
       <c r="M3">
-        <v>8.07</v>
+        <v>9.74</v>
       </c>
       <c r="N3">
-        <v>0.04385869565217392</v>
+        <v>0.06243589743589744</v>
       </c>
       <c r="O3">
-        <v>0.6838983050847457</v>
+        <v>0.6450331125827815</v>
       </c>
       <c r="P3">
-        <v>2.9</v>
+        <v>5.42</v>
       </c>
       <c r="Q3">
-        <v>0.01576086956521739</v>
+        <v>0.03474358974358974</v>
       </c>
       <c r="R3">
-        <v>0.2457627118644068</v>
+        <v>0.3589403973509934</v>
       </c>
       <c r="S3">
-        <v>5.17</v>
+        <v>4.32</v>
       </c>
       <c r="T3">
-        <v>0.6406443618339529</v>
+        <v>0.4435318275154004</v>
       </c>
       <c r="U3">
-        <v>90.5</v>
+        <v>116.2</v>
       </c>
       <c r="V3">
-        <v>0.4918478260869565</v>
+        <v>0.7448717948717949</v>
       </c>
       <c r="W3">
-        <v>0.0960912052117264</v>
+        <v>0.1193675889328063</v>
       </c>
       <c r="X3">
-        <v>0.03798119039409924</v>
+        <v>0.07348037806243042</v>
       </c>
       <c r="Y3">
-        <v>0.05811001481762716</v>
+        <v>0.04588721087037589</v>
       </c>
       <c r="Z3">
-        <v>0.2589547301767319</v>
+        <v>0.4443883348062113</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03326073346042226</v>
+        <v>0.07253347726182223</v>
       </c>
       <c r="AC3">
-        <v>-0.03326073346042226</v>
+        <v>-0.07253347726182223</v>
       </c>
       <c r="AD3">
-        <v>49.9</v>
+        <v>19.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>49.9</v>
+        <v>19.2</v>
       </c>
       <c r="AG3">
-        <v>-40.6</v>
+        <v>-97</v>
       </c>
       <c r="AH3">
-        <v>0.2133390337751176</v>
+        <v>0.1095890410958904</v>
       </c>
       <c r="AI3">
-        <v>0.2828798185941043</v>
+        <v>0.1270681667769689</v>
       </c>
       <c r="AJ3">
-        <v>-0.2831241283124128</v>
+        <v>-1.64406779661017</v>
       </c>
       <c r="AK3">
-        <v>-0.4726426076833527</v>
+        <v>-2.779369627507163</v>
       </c>
       <c r="AL3">
         <v>0</v>
